--- a/artfynd/A 21038-2023 artfynd.xlsx
+++ b/artfynd/A 21038-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21038-2023 artfynd.xlsx
+++ b/artfynd/A 21038-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112845420</v>
+        <v>112845429</v>
       </c>
       <c r="B2" t="n">
-        <v>91197</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,8 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651875</v>
+        <v>651708</v>
       </c>
       <c r="R2" t="n">
-        <v>6677590</v>
+        <v>6677602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,6 +760,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112845425</v>
+        <v>112845386</v>
       </c>
       <c r="B3" t="n">
-        <v>91226</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,37 +811,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651914</v>
+        <v>651863</v>
       </c>
       <c r="R3" t="n">
-        <v>6677525</v>
+        <v>6677626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112845423</v>
+        <v>112845387</v>
       </c>
       <c r="B4" t="n">
-        <v>91226</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,37 +917,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,7 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651907</v>
+        <v>651562</v>
       </c>
       <c r="R4" t="n">
-        <v>6677539</v>
+        <v>6677717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,6 +996,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1005,15 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112845427</v>
+        <v>112845411</v>
       </c>
       <c r="B5" t="n">
-        <v>91217</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,14 +1060,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 3,1 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651929</v>
+        <v>651921</v>
       </c>
       <c r="R5" t="n">
-        <v>6677474</v>
+        <v>6677858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,15 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112845426</v>
+        <v>112845413</v>
       </c>
       <c r="B6" t="n">
-        <v>91226</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,14 +1165,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 3,1 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,8 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651938</v>
+        <v>651964</v>
       </c>
       <c r="R6" t="n">
-        <v>6677517</v>
+        <v>6677873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,15 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112845431</v>
+        <v>112845415</v>
       </c>
       <c r="B7" t="n">
-        <v>89720</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,14 +1270,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 2,8 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651650</v>
+        <v>651976</v>
       </c>
       <c r="R7" t="n">
-        <v>6677647</v>
+        <v>6677845</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,12 +1344,7 @@
         <v>112845430</v>
       </c>
       <c r="B8" t="n">
-        <v>89720</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,15 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112845419</v>
+        <v>112845431</v>
       </c>
       <c r="B9" t="n">
-        <v>91226</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,14 +1480,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,8 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651875</v>
+        <v>651651</v>
       </c>
       <c r="R9" t="n">
-        <v>6677590</v>
+        <v>6677646</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,42 +1551,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112845362</v>
+        <v>112845420</v>
       </c>
       <c r="B10" t="n">
-        <v>104230</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1598,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651928</v>
+        <v>651875</v>
       </c>
       <c r="R10" t="n">
-        <v>6677519</v>
+        <v>6677590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,54 +1656,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112845386</v>
+        <v>112845421</v>
       </c>
       <c r="B11" t="n">
-        <v>93638</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2813</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651862</v>
+        <v>651888</v>
       </c>
       <c r="R11" t="n">
-        <v>6677626</v>
+        <v>6677575</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,37 +1761,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112845410</v>
+        <v>112845418</v>
       </c>
       <c r="B12" t="n">
-        <v>91226</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1815,14 +1795,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651958</v>
+        <v>651875</v>
       </c>
       <c r="R12" t="n">
-        <v>6677825</v>
+        <v>6677590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,15 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112845429</v>
+        <v>112845427</v>
       </c>
       <c r="B13" t="n">
-        <v>89944</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,14 +1900,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 2,8 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 3,1 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651708</v>
+        <v>651928</v>
       </c>
       <c r="R13" t="n">
-        <v>6677602</v>
+        <v>6677474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,26 +1951,6 @@
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Död trädstam</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Dead tree stem # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2016,37 +1971,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112845418</v>
+        <v>112845410</v>
       </c>
       <c r="B14" t="n">
-        <v>91217</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2055,14 +2005,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651875</v>
+        <v>651958</v>
       </c>
       <c r="R14" t="n">
-        <v>6677590</v>
+        <v>6677825</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,19 +2076,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112845428</v>
+        <v>112845416</v>
       </c>
       <c r="B15" t="n">
-        <v>91226</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2151,12 +2096,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,14 +2110,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 2,8 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651777</v>
+        <v>651978</v>
       </c>
       <c r="R15" t="n">
-        <v>6677555</v>
+        <v>6677863</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,37 +2181,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112845411</v>
+        <v>112845419</v>
       </c>
       <c r="B16" t="n">
-        <v>89720</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2275,14 +2215,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
+          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651921</v>
+        <v>651875</v>
       </c>
       <c r="R16" t="n">
-        <v>6677858</v>
+        <v>6677590</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,6 +2279,1174 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112845423</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>651908</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6677540</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112845425</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>651914</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6677524</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112845426</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 3,1 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>651938</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6677517</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112845428</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>651776</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6677555</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>71906708</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mariebo, Stubbokärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>651829</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6677559</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-06-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-06-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mattias Björkman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mattias Björkman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112845360</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>652005</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6677757</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>112845358</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 2,9 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>651880</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6677643</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112845362</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 3,0 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>651928</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6677519</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112845365</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 2,6 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>651622</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6677819</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112845367</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 2,6 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>651680</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6677850</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112845364</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Örbyhus kyrka, 2,6 km SO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>651622</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6677819</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>

--- a/artfynd/A 21038-2023 artfynd.xlsx
+++ b/artfynd/A 21038-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -795,6 +800,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845429</t>
         </is>
       </c>
     </row>
@@ -903,6 +913,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845386</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845387</t>
         </is>
       </c>
     </row>
@@ -1128,6 +1148,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845411</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845415</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845430</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845431</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845421</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845418</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845427</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845410</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845416</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2283,6 +2358,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845419</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2388,6 +2468,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845423</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2493,6 +2578,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845425</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845426</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2703,6 +2798,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845428</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71906708</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2924,6 +3029,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845360</t>
         </is>
       </c>
     </row>
@@ -3031,6 +3141,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845358</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3136,6 +3251,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845362</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3241,6 +3361,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845365</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3346,6 +3471,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845367</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3451,8 +3581,41 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112845364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>